--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jul-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jul-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>79843.36</v>
+        <v>80565.07000000001</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>32092.15</v>
+        <v>32382.23</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1690339.34</v>
+        <v>1696277.88</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>450579.75</v>
+        <v>452162.74</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>33018.3</v>
+        <v>33134.3</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>10195.69</v>
+        <v>10231.51</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>29627.47</v>
+        <v>29915.81</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>132104.82</v>
+        <v>133390.47</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>22031.5</v>
+        <v>22245.91</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>7692.5</v>
+        <v>7768.58</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>15803.64</v>
+        <v>15959.94</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>48432.45</v>
+        <v>48676.54</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>36324.34</v>
+        <v>36507.4</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>24479.45</v>
+        <v>24602.81</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>76240.75</v>
+        <v>76538.36</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>13055.7</v>
+        <v>13106.67</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>17021.55</v>
+        <v>16936.63</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>26703</v>
+        <v>26569.78</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>481036.15</v>
+        <v>482098.69</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>54890.11</v>
+        <v>55011.36</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>8939.08</v>
+        <v>8998.049999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>18359.58</v>
+        <v>18480.71</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>37434.5</v>
+        <v>37523.24</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>38324.81</v>
+        <v>38415.67</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>52468.49</v>
+        <v>52823.77</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>30383.47</v>
+        <v>30598.47</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>20172.12</v>
+        <v>20314.86</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>17290.32</v>
+        <v>17412.68</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>7466.23</v>
+        <v>7443.22</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>37342.12</v>
+        <v>37227.05</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>7209.65</v>
+        <v>7187.44</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>15862.68</v>
+        <v>15813.8</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>42042.6</v>
+        <v>41954.37</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>14031.21</v>
+        <v>14001.76</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>914845.87</v>
+        <v>913082.5600000001</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>8159.82</v>
+        <v>8144.09</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>32529.1</v>
+        <v>32466.41</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>7262.24</v>
+        <v>7248.24</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>48028.85</v>
+        <v>47936.28</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>8249.17</v>
+        <v>8202.049999999999</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>15788.59</v>
+        <v>15535.01</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>69753.46000000001</v>
+        <v>68633.12</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>46263.52</v>
+        <v>45525.27</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>10103.26</v>
+        <v>9942.030000000001</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>98707.45</v>
+        <v>97132.32000000001</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>10638.47</v>
+        <v>10468.71</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>79253.71000000001</v>
+        <v>78337.60000000001</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>50854.08</v>
+        <v>50266.24</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>15789.24</v>
+        <v>15606.73</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>21540.28</v>
+        <v>21436.03</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>261926.13</v>
+        <v>260658.45</v>
       </c>
     </row>
     <row r="53">
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>10530.05</v>
+        <v>10479.08</v>
       </c>
     </row>
     <row r="54">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>45879.04</v>
+        <v>45656.99</v>
       </c>
     </row>
     <row r="55">
@@ -3810,7 +3810,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>17460.36</v>
+        <v>17375.86</v>
       </c>
     </row>
     <row r="56">
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>17390.62</v>
+        <v>17306.45</v>
       </c>
     </row>
     <row r="57">
@@ -3932,7 +3932,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>12085.64</v>
+        <v>12167.48</v>
       </c>
     </row>
     <row r="58">
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>19991.55</v>
+        <v>20126.92</v>
       </c>
     </row>
     <row r="59">
@@ -4054,7 +4054,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>134762.36</v>
+        <v>135674.88</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jul-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jul-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jul-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jul-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jul-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jul-2026.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Subsecretaria de Transportes</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ANDESTIC SPA</t>
+          <t>Andestic SpA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>GEORG</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>LAHUEN HEALTH SERVICES SPA</t>
+          <t>Lahuen Health Services SpA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>GEORG</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jul-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jul-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>77.146.212-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>76.286.397-9</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>96.986.170-4</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>76.891.821-k</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1005,11 @@
           <t>96.799.250-k</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1070,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1135,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1200,11 @@
           <t>76.504.980-6</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1326,11 @@
           <t>77.146.212-K</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1391,11 @@
           <t>77.146.212-K</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1456,11 @@
           <t>92.580.000-7</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1582,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1769,11 @@
           <t>77.754.348-2</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1895,11 @@
           <t>76.891.821-k</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2021,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2086,11 @@
           <t>77.146.212-K</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2151,11 @@
           <t>77.799.671-1</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2344,7 +2412,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4343-131-CM26</t>
+          <t>1499-2468-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2369,43 +2437,47 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.606.912-8</t>
+          <t>61.608.402-k</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
+          <t>INSTITUTO NACIONAL DEL TORAX</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Georg</t>
+          <t>Lahuen Health Services SpA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.624.276-6</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>76.227.643-7</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>7187.44</v>
+        <v>15813.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1499-2468-CM26</t>
+          <t>4343-131-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2430,37 +2502,41 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.608.402-k</t>
+          <t>61.606.912-8</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DEL TORAX</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Lahuen Health Services SpA</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.227.643-7</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>76.624.276-6</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>15813.8</v>
+        <v>7187.44</v>
       </c>
     </row>
     <row r="34">
@@ -2758,7 +2834,11 @@
           <t>76.891.821-k</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2899,11 @@
           <t>77.347.464-8</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2964,11 @@
           <t>76.891.821-k</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3029,11 @@
           <t>76.624.276-6</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3216,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3281,11 @@
           <t>76.334.381-2</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3346,11 @@
           <t>77.173.545-2</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3411,11 @@
           <t>76.260.080-3</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3476,11 @@
           <t>77.363.384-3</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3541,11 @@
           <t>77.063.770-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3606,11 @@
           <t>96.777.670-k</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3503,7 +3623,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4666-1-CM26</t>
+          <t>2455-107-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3528,12 +3648,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>60.901.000-2</t>
+          <t>69.071.000-5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUINTA NORMAL</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3543,28 +3663,32 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>USERCODE SPA</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>77.347.464-8</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>21436.03</v>
+        <v>260658.45</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2455-107-CM26</t>
+          <t>711841-231-SE26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3589,12 +3713,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.071.000-5</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUINTA NORMAL</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,28 +3728,32 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>ALTAVOZ SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>96.827.350-7</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>260658.45</v>
+        <v>10479.08</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>711841-231-SE26</t>
+          <t>869591-36-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3650,12 +3778,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>60.808.000-7</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3793,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>ALTAVOZ SOCIEDAD ANONIMA</t>
+          <t>XMS Business Solutions S.A.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>96.827.350-7</t>
+          <t>76.249.938-k</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3684,13 +3812,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>10479.08</v>
+        <v>45656.99</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>869591-36-CM26</t>
+          <t>711841-243-SE26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3715,12 +3843,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>60.808.000-7</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3730,28 +3858,32 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>XMS Business Solutions S.A.</t>
+          <t>ANTICIPA S A</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.249.938-k</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
+          <t>96.771.610-3</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>45656.99</v>
+        <v>17375.86</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>711841-243-SE26</t>
+          <t>4666-1-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3776,12 +3908,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>60.901.000-2</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3791,12 +3923,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>ANTICIPA S A</t>
+          <t>USERCODE SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>96.771.610-3</t>
+          <t>77.347.464-8</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3810,7 +3942,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>17375.86</v>
+        <v>21436.03</v>
       </c>
     </row>
     <row r="56">
@@ -3986,7 +4118,11 @@
           <t>76.891.821-k</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3999,61 +4135,195 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>709603-146-SE26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>61.980.220-9</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>SUPERINTENDENCIA DE EDUCACION ESCOLAR</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>XMS Business Solutions S.A.</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>76.249.938-k</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>36358.3</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>709603-147-SE26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>61.980.220-9</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>SUPERINTENDENCIA DE EDUCACION ESCOLAR</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>XMS TECHNOLOGIES S.A.</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>76.083.145-k</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>32462.77</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>606-299-CM26</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>jul-2026</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>60.513.000-3</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
         <is>
           <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>77.063.770-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="n">
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
         <v>135674.88</v>
       </c>
     </row>

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jul-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jul-2026.xlsx
@@ -1708,7 +1708,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jul-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jul-2026.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
